--- a/2025-MLS-projections/Scenarios/MLS_Rebuilding_Catch_Tables.xlsx
+++ b/2025-MLS-projections/Scenarios/MLS_Rebuilding_Catch_Tables.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jon.brodziak\Desktop\2024 WCNPO MLS Rebuilding\2025 MLS projections\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jon.brodziak\Desktop\2024 WCNPO MLS Rebuilding\2025 MLS projections\Scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53306884-9BD5-4B8C-80CD-C409832D471E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{225AF1F8-B3E7-4D89-8012-D984E5614323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="8863" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1183" yWindow="634" windowWidth="13766" windowHeight="8186" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="14">
   <si>
     <t>Country</t>
   </si>
@@ -66,6 +66,15 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>Scenario 1. No Carryover Catch</t>
+  </si>
+  <si>
+    <t>Scenario 2. Carryover Catch in 2025</t>
+  </si>
+  <si>
+    <t>Scenario 3. Carryover Catch in 2025-2026</t>
   </si>
 </sst>
 </file>
@@ -97,7 +106,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -106,17 +115,151 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
+      <left style="medium">
+        <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
+      <top style="medium">
+        <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -124,10 +267,70 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -467,252 +670,263 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="14.765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D2" s="21" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B2">
+      <c r="B3" s="12">
         <v>1454.4</v>
       </c>
-      <c r="C2">
+      <c r="C3" s="27">
         <v>1454.4</v>
       </c>
-      <c r="D2">
+      <c r="D3" s="13">
         <v>1454.4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B3">
+      <c r="B4" s="14">
         <v>358.4</v>
       </c>
-      <c r="C3">
+      <c r="C4" s="28">
         <v>358.4</v>
       </c>
-      <c r="D3">
+      <c r="D4" s="15">
         <v>358.4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A5" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B4">
+      <c r="B5" s="14">
         <v>214.8</v>
       </c>
-      <c r="C4">
+      <c r="C5" s="28">
         <v>214.8</v>
       </c>
-      <c r="D4">
+      <c r="D5" s="15">
         <v>214.8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B5">
+      <c r="B6" s="14">
         <v>228.4</v>
       </c>
-      <c r="C5">
+      <c r="C6" s="28">
         <v>228.4</v>
       </c>
-      <c r="D5">
+      <c r="D6" s="15">
         <v>228.4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A7" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B6">
+      <c r="B7" s="14">
         <v>68.8</v>
       </c>
-      <c r="C6">
+      <c r="C7" s="28">
         <v>68.8</v>
       </c>
-      <c r="D6">
+      <c r="D7" s="15">
         <v>68.8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
+    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B7">
+      <c r="B8" s="16">
         <v>75.2</v>
       </c>
-      <c r="C7">
+      <c r="C8" s="29">
         <v>75.2</v>
       </c>
-      <c r="D7">
+      <c r="D8" s="17">
         <v>75.2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
+    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B8">
+      <c r="B9" s="18">
         <v>2400</v>
       </c>
-      <c r="C8">
+      <c r="C9" s="24">
         <v>2400</v>
       </c>
-      <c r="D8">
+      <c r="D9" s="19">
         <v>2400</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="14.69140625" customWidth="1"/>
     <col min="2" max="2" width="9.15234375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D2" s="21" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B2">
+      <c r="B3" s="12">
         <f>1454.4 + 165</f>
         <v>1619.4</v>
       </c>
-      <c r="C2">
+      <c r="C3" s="27">
         <v>1454.4</v>
       </c>
-      <c r="D2">
+      <c r="D3" s="13">
         <v>1454.4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3">
+      <c r="B4" s="14">
         <f>358.4 + 165</f>
         <v>523.4</v>
       </c>
-      <c r="C3">
+      <c r="C4" s="28">
         <v>358.4</v>
       </c>
-      <c r="D3">
+      <c r="D4" s="15">
         <v>358.4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4">
+      <c r="B5" s="14">
         <f>214.8 + 165</f>
         <v>379.8</v>
       </c>
-      <c r="C4">
+      <c r="C5" s="28">
         <v>214.8</v>
       </c>
-      <c r="D4">
+      <c r="D5" s="15">
         <v>214.8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5">
+      <c r="B6" s="14">
         <f>228.4 + 165</f>
         <v>393.4</v>
       </c>
-      <c r="C5">
+      <c r="C6" s="28">
         <v>228.4</v>
       </c>
-      <c r="D5">
+      <c r="D6" s="15">
         <v>228.4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6">
+      <c r="B7" s="14">
         <f>68.8 + 165</f>
         <v>233.8</v>
       </c>
-      <c r="C6">
+      <c r="C7" s="28">
         <v>68.8</v>
       </c>
-      <c r="D6">
+      <c r="D7" s="15">
         <v>68.8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
+    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B7">
+      <c r="B8" s="16">
         <v>75.2</v>
       </c>
-      <c r="C7">
+      <c r="C8" s="29">
         <v>75.2</v>
       </c>
-      <c r="D7">
+      <c r="D8" s="17">
         <v>75.2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
+    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B8">
+      <c r="B9" s="16">
         <v>3225</v>
       </c>
-      <c r="C8">
+      <c r="C9" s="24">
         <v>2400</v>
       </c>
-      <c r="D8">
+      <c r="D9" s="17">
         <v>2400</v>
       </c>
     </row>
@@ -723,131 +937,136 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="14.53515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D2" s="21" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B2">
+      <c r="B3" s="6">
         <f>1454.4 + 165</f>
         <v>1619.4</v>
       </c>
-      <c r="C2">
+      <c r="C3" s="8">
         <f>1454.4 + 165</f>
         <v>1619.4</v>
       </c>
-      <c r="D2">
+      <c r="D3" s="7">
         <v>1454.4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B3">
+      <c r="B4" s="1">
         <f>358.4 + 165</f>
         <v>523.4</v>
       </c>
-      <c r="C3">
+      <c r="C4" s="9">
         <f>358.4 + 165</f>
         <v>523.4</v>
       </c>
-      <c r="D3">
+      <c r="D4" s="2">
         <v>358.4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A5" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B4">
+      <c r="B5" s="1">
         <f>214.8 + 165</f>
         <v>379.8</v>
       </c>
-      <c r="C4">
+      <c r="C5" s="9">
         <f>214.8 + 165</f>
         <v>379.8</v>
       </c>
-      <c r="D4">
+      <c r="D5" s="2">
         <v>214.8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B5">
+      <c r="B6" s="1">
         <f>228.4 + 165</f>
         <v>393.4</v>
       </c>
-      <c r="C5">
+      <c r="C6" s="9">
         <f>228.4 + 165</f>
         <v>393.4</v>
       </c>
-      <c r="D5">
+      <c r="D6" s="2">
         <v>228.4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A7" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B6">
+      <c r="B7" s="1">
         <f>68.8 + 165</f>
         <v>233.8</v>
       </c>
-      <c r="C6">
+      <c r="C7" s="9">
         <f>68.8 + 165</f>
         <v>233.8</v>
       </c>
-      <c r="D6">
+      <c r="D7" s="2">
         <v>68.8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
+    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B7">
+      <c r="B8" s="3">
         <v>75.2</v>
       </c>
-      <c r="C7">
+      <c r="C8" s="10">
         <v>75.2</v>
       </c>
-      <c r="D7">
+      <c r="D8" s="5">
         <v>75.2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
+    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B8">
+      <c r="B9" s="4">
         <v>3225</v>
       </c>
-      <c r="C8">
+      <c r="C9" s="26">
         <v>3225</v>
       </c>
-      <c r="D8">
+      <c r="D9" s="5">
         <v>2400</v>
       </c>
     </row>
